--- a/output/pdf_financials_xlsx/DMCU.xlsx
+++ b/output/pdf_financials_xlsx/DMCU.xlsx
@@ -4762,31 +4762,31 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.238847</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.510661</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.510661</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.027387</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.168634</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.168634</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.168634</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.291556</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.705242</v>
       </c>
     </row>
     <row r="93">
@@ -5238,7 +5238,7 @@
         <v>-0.332935</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>0.229684</v>
       </c>
       <c r="H103" s="3" t="n">
         <v>0</v>
@@ -5931,25 +5931,25 @@
         <v>-2.018381</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>1.075875</v>
+        <v>-0.252516</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.750611</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-2.769779</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-1.707681</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>1.234766</v>
+        <v>0.993959</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>4.260584</v>
+        <v>3.776399</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.897584</v>
       </c>
     </row>
     <row r="119">
@@ -8149,7 +8149,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -8795,7 +8799,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -9741,7 +9749,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -10458,7 +10470,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -11570,7 +11586,11 @@
           <t>Prepaid and deposits 833</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -12550,7 +12570,11 @@
           <t>Reserves 7 973,103</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -13429,7 +13453,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -13990,7 +14018,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -14871,7 +14903,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -17437,7 +17473,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -23778,7 +23818,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DMCU.xlsx
+++ b/output/pdf_financials_xlsx/DMCU.xlsx
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.010197</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>-1.403621</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.925458</v>
+        <v>-1.935655</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-3.541264</v>
@@ -1762,7 +1762,7 @@
         <v>-1.403621</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.911248</v>
+        <v>-1.921445</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-3.523764</v>
@@ -1993,22 +1993,22 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.002246</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>7.7e-05</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.196987</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.397728</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.24182</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.22523</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>1.140337</v>
@@ -2023,10 +2023,10 @@
         <v>0.172412</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.071834</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.155114</v>
       </c>
     </row>
     <row r="35">
@@ -2085,22 +2085,22 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.002246</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>7.7e-05</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.196987</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.397728</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.24182</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.22523</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1.140337</v>
@@ -2115,10 +2115,10 @@
         <v>0.172412</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.071834</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.155114</v>
       </c>
     </row>
     <row r="37">
@@ -2637,22 +2637,22 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.002246</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.196987</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.730663</v>
+        <v>0.332935</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.345071</v>
+        <v>0.103251</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.328481</v>
+        <v>0.103251</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -2667,10 +2667,10 @@
         <v>0.001042</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.081349</v>
+        <v>0.009514999999999999</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.631313</v>
+        <v>0.476199</v>
       </c>
     </row>
     <row r="49">
@@ -6228,10 +6228,10 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0075</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.036521</v>
       </c>
     </row>
     <row r="125">
@@ -6274,10 +6274,10 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0075</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.036521</v>
       </c>
     </row>
     <row r="126">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -13297,7 +13297,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -17937,7 +17937,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -30856,7 +30860,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -34370,7 +34374,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -39143,7 +39147,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
